--- a/output/power_ratings_final.xlsx
+++ b/output/power_ratings_final.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T138"/>
+  <dimension ref="A1:U138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -429,21 +429,22 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,75 +475,80 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>early_season_rating_scale</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>efficiency_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>schedule_score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_team_postgame_elo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>fbs_win_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>fbs_avg_margin</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>fbs_avg_opponent_pregame_elo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>avg_cover_margin</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>offense_ppa</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>defense_ppa_allowed</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>wepa_total</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>wepa_allowed_total</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>talent</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ap_latest_rank</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>cfp_latest_rank</t>
         </is>
@@ -573,48 +579,51 @@
         <v>18.51</v>
       </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>58.93</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>96.22</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>89.39</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2041</v>
       </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
       <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
         <v>28</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1501</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>7.167</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>0.349068</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.071745</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>953.03</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -641,48 +650,51 @@
         <v>18.23</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>81.87</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>93.09</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>79.2</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2022</v>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
       <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
         <v>53</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1173</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2.667</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0.6666069999999999</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>-0.242325</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>964.27</v>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -709,48 +721,51 @@
         <v>17.1</v>
       </c>
       <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>52.62</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>95.19</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>86.73999999999999</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1877</v>
       </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>7</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1562</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>-17.667</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0.27709</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0.11263</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>984.33</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>2</v>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -777,48 +792,51 @@
         <v>16.8</v>
       </c>
       <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>70.44</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>88.02</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>98.89</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2132</v>
       </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>36</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1639</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>-3.833</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>0.653558</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>0.134556</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>735.26</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -845,48 +863,51 @@
         <v>15.77</v>
       </c>
       <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
         <v>76.38</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>79.33</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>87.27</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1808</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
         <v>27.5</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1471.5</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>-2.083</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>0.363397</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>-0.027366</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>899</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>14</v>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -913,48 +934,51 @@
         <v>15.25</v>
       </c>
       <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
         <v>66.16</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>82.52</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>98.16</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1921</v>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
       <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
         <v>52</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1570</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>22.5</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>0.458651</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0.139052</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>985.17</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>5</v>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -981,48 +1005,51 @@
         <v>14.02</v>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>64.5</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>81.06</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>94.43000000000001</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>1829</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
       <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
         <v>38</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1562</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>10</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>0.292156</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-0.198543</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>973.53</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>13</v>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1049,48 +1076,51 @@
         <v>13.84</v>
       </c>
       <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
         <v>71.27</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>81.14</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>86.70999999999999</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1930</v>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
       <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
         <v>39</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1408</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>14.5</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>0.461253</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>0.019904</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>885.9400000000001</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>7</v>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1117,48 +1147,51 @@
         <v>13.4</v>
       </c>
       <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
         <v>71.18000000000001</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>78.81999999999999</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>88.41</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>1865</v>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
       <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
         <v>50</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1385</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>10.833</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>0.351323</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-0.244122</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>933</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>8</v>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1185,48 +1218,51 @@
         <v>13.31</v>
       </c>
       <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
         <v>49.06</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>84.12</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>90.69</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1837</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>1666</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>-3.5</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>0.297674</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.388619</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>885.72</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>9</v>
       </c>
-      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1253,13 +1289,13 @@
         <v>13.09</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1274,27 +1310,30 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>10.667</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>0.743277</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>-0.098493</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>1003.67</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1321,48 +1360,51 @@
         <v>10.95</v>
       </c>
       <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
         <v>54.13</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>78.76000000000001</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>82.7</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1686</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>1530</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-26.5</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>0.235518</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>-0.036869</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>890.02</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>16</v>
       </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1389,48 +1431,51 @@
         <v>10.67</v>
       </c>
       <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
         <v>81.3</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>71.04000000000001</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>82.08</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1819</v>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
       <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
         <v>51</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1256</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>10.333</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>0.387191</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>-0.251351</v>
       </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>851.14</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>10</v>
       </c>
-      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1457,48 +1502,51 @@
         <v>10.57</v>
       </c>
       <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
         <v>71.37</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>92.11</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>1905</v>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
       <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
         <v>45</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>1478</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>21.667</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>0.422096</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>-0.167851</v>
       </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>774.04</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>18</v>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1525,48 +1573,51 @@
         <v>10.19</v>
       </c>
       <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
         <v>74.48</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>67.48999999999999</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>100</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>1736</v>
       </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
       <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
         <v>41</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>1670</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>31</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>0.418685</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>-0.267877</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>931.76</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1593,48 +1644,51 @@
         <v>9.449999999999999</v>
       </c>
       <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
         <v>50.76</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>72.09</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>91.45</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>1764</v>
       </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
       <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>14</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>1619</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-9.333</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>0.077972</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>-0.032738</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>777.63</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1661,45 +1715,48 @@
         <v>9.06</v>
       </c>
       <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
         <v>90.78</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>65.42</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>78.75</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>1763</v>
       </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
       <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>57</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>1167</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>21.167</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>0.683177</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>-0.038077</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>862.87</v>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1726,14 +1783,14 @@
         <v>8.68</v>
       </c>
       <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
         <v>62.38</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>89.77</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -1747,27 +1804,30 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>-22.167</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>0.27853</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>-0.138025</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>767.89</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>12</v>
       </c>
-      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1794,48 +1854,51 @@
         <v>8.279999999999999</v>
       </c>
       <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
         <v>48.16</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>68.47</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>83.02</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>1868</v>
       </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
       <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
         <v>40</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>1322</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>8.333</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>0.061317</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>-0.331732</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>722.73</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>22</v>
       </c>
-      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1862,45 +1925,48 @@
         <v>7.73</v>
       </c>
       <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>63.46</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>81.55</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>1669</v>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
       <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
         <v>45</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>1285</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>18.833</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>0.621458</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>0.107901</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>891.0700000000001</v>
       </c>
-      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1927,14 +1993,14 @@
         <v>7.46</v>
       </c>
       <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
         <v>78.47</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>82.48999999999999</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -1948,27 +2014,30 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>-2.333</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>0.569198</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>-0.126154</v>
       </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>885.9</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>20</v>
       </c>
-      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1995,45 +2064,48 @@
         <v>7.18</v>
       </c>
       <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
         <v>11.63</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>76.34999999999999</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>1550</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>-41</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>1616</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-31</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>-0.267877</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>0.418685</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>862.85</v>
       </c>
-      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2060,48 +2132,51 @@
         <v>6.41</v>
       </c>
       <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
         <v>55.88</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>62.96</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>97.41</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>1668</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>-3</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>1839</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>3.5</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>0.388619</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>0.297674</v>
       </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>739.97</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>24</v>
       </c>
-      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2128,45 +2203,48 @@
         <v>6.33</v>
       </c>
       <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
         <v>42.11</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>66.79000000000001</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>81.36</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>1610</v>
       </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
         <v>1506</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>-5.5</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>0.028238</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>0.054174</v>
       </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>828.1900000000001</v>
       </c>
-      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2193,14 +2271,14 @@
         <v>6.32</v>
       </c>
       <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
         <v>70.22</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>76.05</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -2214,27 +2292,30 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>14</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>0.510747</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>0.137355</v>
       </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>695.72</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>21</v>
       </c>
-      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2261,14 +2342,14 @@
         <v>5.69</v>
       </c>
       <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
         <v>57.67</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>77.55</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -2282,24 +2363,27 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>-10</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>0.282517</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>0.029045</v>
       </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>727.39</v>
       </c>
-      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2326,14 +2410,14 @@
         <v>5.54</v>
       </c>
       <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
         <v>66.67</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>77.86</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -2347,27 +2431,30 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>-15.5</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>0.378488</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>0.016518</v>
       </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>808.36</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>25</v>
       </c>
-      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2394,45 +2481,48 @@
         <v>5.19</v>
       </c>
       <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
         <v>50.13</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>59.96</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>93.87</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>1776</v>
       </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
       <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
         <v>7</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>1703</v>
       </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
       <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
         <v>0.279763</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>0.028036</v>
       </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>588.3099999999999</v>
       </c>
-      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2459,45 +2549,48 @@
         <v>4.89</v>
       </c>
       <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
         <v>40.96</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>62.84</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>77.93000000000001</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1686</v>
       </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
       <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
         <v>10</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>1382</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>-4.5</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>-0.062746</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>0.110655</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>703.8099999999999</v>
       </c>
-      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2524,45 +2617,48 @@
         <v>4.78</v>
       </c>
       <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>57.75</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>81.84</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>1597</v>
       </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
       <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
         <v>28</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>1372</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>4.333</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>0.492529</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>0.127526</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>787.45</v>
       </c>
-      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2589,45 +2685,48 @@
         <v>4.65</v>
       </c>
       <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
         <v>49.18</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>61.49</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>1559</v>
       </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
       <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
         <v>17</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>1281</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>-14</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>0.290662</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>0.162657</v>
       </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>800.2</v>
       </c>
-      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2654,45 +2753,48 @@
         <v>4.34</v>
       </c>
       <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
         <v>77.08</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>55.74</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>83.3</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1597</v>
       </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
       <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
         <v>19</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>1443</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>-6.833</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>0.529351</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>0.139131</v>
       </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>704.01</v>
       </c>
-      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2719,45 +2821,48 @@
         <v>3.75</v>
       </c>
       <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
         <v>79.67</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>52.39</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>76.76000000000001</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>1597</v>
       </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
       <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
         <v>49</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>1177</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>20.5</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>0.638028</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>-0.025209</v>
       </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>804.53</v>
       </c>
-      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2784,45 +2889,48 @@
         <v>3.65</v>
       </c>
       <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
         <v>30.54</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>59.09</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>92.51000000000001</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>1697</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>-7</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>1770</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>-1</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>0.028036</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>0.279763</v>
       </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>633.35</v>
       </c>
-      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2849,45 +2957,48 @@
         <v>3.6</v>
       </c>
       <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
         <v>63.41</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>52.66</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>1652</v>
       </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
       <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
         <v>26</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>1570</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>22</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>0.272622</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>-0.14384</v>
       </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>700.1799999999999</v>
       </c>
-      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2914,45 +3025,48 @@
         <v>3.53</v>
       </c>
       <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
         <v>37.47</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>61.64</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>72.81</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>1598</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>-5</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>1380</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>-12.5</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>-0.045869</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>0.107152</v>
       </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>730.79</v>
       </c>
-      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2979,14 +3093,14 @@
         <v>3.32</v>
       </c>
       <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
         <v>89.65000000000001</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>66.91</v>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -3000,27 +3114,30 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>5.833</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>0.54247</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>-0.109228</v>
       </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>689.42</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>14</v>
       </c>
-      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3047,45 +3164,48 @@
         <v>3.11</v>
       </c>
       <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
         <v>25.77</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>62.36</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>78.06999999999999</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>1509</v>
       </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>-26</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>1591</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>-22</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>-0.14384</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>0.272622</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>757.14</v>
       </c>
-      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3112,45 +3232,48 @@
         <v>3.06</v>
       </c>
       <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
         <v>41.29</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>59.1</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>74.91</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>1555</v>
       </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>-1</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>1396</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>-7.5</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>0.074022</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>0.052211</v>
       </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
         <v>751.65</v>
       </c>
-      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3177,14 +3300,14 @@
         <v>2.91</v>
       </c>
       <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
         <v>91.84999999999999</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>62.28</v>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -3198,24 +3321,27 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>26.667</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>0.587894</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>-0.276078</v>
       </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>718.67</v>
       </c>
-      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3242,14 +3368,14 @@
         <v>2.73</v>
       </c>
       <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
         <v>68.51000000000001</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>66.44</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -3263,24 +3389,27 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
         <v>-4.5</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>0.216206</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>-0.228626</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
         <v>699.59</v>
       </c>
-      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3307,45 +3436,48 @@
         <v>2.71</v>
       </c>
       <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
         <v>34.74</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>56.43</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>98.22</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>1455</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>-28</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>1995</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>-7.167</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>0.071745</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>0.349068</v>
       </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>767.6799999999999</v>
       </c>
-      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3372,45 +3504,48 @@
         <v>2.43</v>
       </c>
       <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
         <v>64.56</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>48.86</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>85.55</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>1688</v>
       </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
       <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
         <v>45</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>1364</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>28.667</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>0.426656</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>0.114011</v>
       </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
         <v>675.02</v>
       </c>
-      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3437,45 +3572,48 @@
         <v>2.42</v>
       </c>
       <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
         <v>40.45</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>54.8</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>81.3</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>1582.5</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>0.5</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>4.5</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>1490</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>0.833</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>0.120026</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>0.089285</v>
       </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
         <v>696.03</v>
       </c>
-      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3502,45 +3640,48 @@
         <v>2.15</v>
       </c>
       <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
         <v>63.35</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>49.36</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>83.08</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>1555.5</v>
       </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
       <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
         <v>12</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>1479.5</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>9</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>0.394294</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>0.105805</v>
       </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
         <v>670.3099999999999</v>
       </c>
-      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3567,14 +3708,14 @@
         <v>2.13</v>
       </c>
       <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
         <v>82.73999999999999</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>60.76</v>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -3588,24 +3729,27 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
         <v>19</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>0.681106</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>-0.054372</v>
       </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
         <v>722</v>
       </c>
-      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3632,14 +3776,14 @@
         <v>2.09</v>
       </c>
       <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
         <v>58.48</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>67.16</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -3653,24 +3797,27 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
         <v>-23.5</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>0.17625</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>-0.074617</v>
       </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>745.48</v>
       </c>
-      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3697,45 +3844,48 @@
         <v>1.62</v>
       </c>
       <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
         <v>26.48</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>52.78</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>87.81999999999999</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>1605</v>
       </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
       <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
         <v>14</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>1555</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>5</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>-0.050566</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>0.004092</v>
       </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>668.47</v>
       </c>
-      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3762,48 +3912,51 @@
         <v>1.52</v>
       </c>
       <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
         <v>59.01</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>52.07</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>72.45</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>1521</v>
       </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
       <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
         <v>13</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>1266</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>-7.833</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>0.312247</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>0.182879</v>
       </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
         <v>695.9299999999999</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>23</v>
       </c>
-      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3830,14 +3983,14 @@
         <v>1.5</v>
       </c>
       <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
         <v>84.06</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>60.01</v>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -3851,24 +4004,27 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
         <v>9.667</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>0.562307</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>0.077241</v>
       </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
         <v>786.65</v>
       </c>
-      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3895,14 +4051,14 @@
         <v>1.42</v>
       </c>
       <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
         <v>42.79</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>61.46</v>
       </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -3916,24 +4072,27 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
         <v>-1.5</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>0.244667</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>-0.059524</v>
       </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
         <v>669.55</v>
       </c>
-      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3960,45 +4119,48 @@
         <v>1.36</v>
       </c>
       <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
         <v>44.1</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>51.71</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>86.02</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>1509</v>
       </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
       <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
         <v>-1</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>1613</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>5.5</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>0.054174</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>0.028238</v>
       </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
         <v>723.28</v>
       </c>
-      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4025,45 +4187,48 @@
         <v>1.13</v>
       </c>
       <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
         <v>37.01</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>52.19</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>89.03</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>1599</v>
       </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
       <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
         <v>-14</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>1744</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>9.333</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>-0.032738</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>0.077972</v>
       </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
         <v>630.29</v>
       </c>
-      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4090,14 +4255,14 @@
         <v>1.08</v>
       </c>
       <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
         <v>74.56</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>58.56</v>
       </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -4111,24 +4276,27 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
         <v>9.5</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>0.342146</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>-0.384009</v>
       </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
         <v>728.79</v>
       </c>
-      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4155,14 +4323,14 @@
         <v>1.07</v>
       </c>
       <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
         <v>69.11</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>59.61</v>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -4176,24 +4344,27 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
         <v>2.5</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>0.479649</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>0.128381</v>
       </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
         <v>688.3200000000001</v>
       </c>
-      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4220,45 +4391,48 @@
         <v>1.01</v>
       </c>
       <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
         <v>70.73999999999999</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>51.45</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>57.37</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>1540</v>
       </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
       <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
         <v>22</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>925</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>-5.5</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>0.477589</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>0.021979</v>
       </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
         <v>680.87</v>
       </c>
-      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4285,45 +4459,48 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
         <v>24.58</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>52.67</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>99.83</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>1571</v>
       </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
       <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
         <v>-36</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>2064</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>3.833</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>0.134556</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>0.653558</v>
       </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
         <v>602.08</v>
       </c>
-      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4350,45 +4527,48 @@
         <v>0.48</v>
       </c>
       <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
         <v>31.18</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>52.71</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>80.47</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>1531</v>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
       <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
         <v>-14</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>1581</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>-5</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>0.004092</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>-0.050566</v>
       </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
         <v>665.11</v>
       </c>
-      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4415,45 +4595,48 @@
         <v>0.46</v>
       </c>
       <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
         <v>36.79</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>48</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>97.98</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>1565</v>
       </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
       <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
         <v>-7</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>1880</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>17.667</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>0.11263</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>0.27709</v>
       </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
         <v>641.17</v>
       </c>
-      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4480,45 +4663,48 @@
         <v>0.42</v>
       </c>
       <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
         <v>46.55</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>57.28</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>49.61</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>1408</v>
       </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
       <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
         <v>-16</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
         <v>978</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>-45.333</v>
       </c>
-      <c r="N61" t="n">
+      <c r="O61" t="n">
         <v>0.203096</v>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>0.329973</v>
       </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
         <v>709.04</v>
       </c>
-      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4545,45 +4731,48 @@
         <v>0.33</v>
       </c>
       <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
         <v>38.51</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>54.24</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>81.84</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>1433</v>
       </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
       <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
         <v>-52</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>1784</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>-22.5</v>
       </c>
-      <c r="N62" t="n">
+      <c r="O62" t="n">
         <v>0.139052</v>
       </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
         <v>0.458651</v>
       </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
         <v>624.8099999999999</v>
       </c>
-      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4610,14 +4799,14 @@
         <v>0.25</v>
       </c>
       <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
         <v>79.59</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>56.96</v>
       </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -4631,24 +4820,27 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
         <v>1.333</v>
       </c>
-      <c r="N63" t="n">
+      <c r="O63" t="n">
         <v>0.569043</v>
       </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
         <v>-0.176148</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
         <v>684.51</v>
       </c>
-      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4675,45 +4867,48 @@
         <v>0.25</v>
       </c>
       <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
         <v>66.75</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>45.05</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>80.84</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>1441</v>
       </c>
-      <c r="J64" t="n">
-        <v>1</v>
-      </c>
       <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
         <v>21</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>1406</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>18.5</v>
       </c>
-      <c r="N64" t="n">
+      <c r="O64" t="n">
         <v>0.419785</v>
       </c>
-      <c r="O64" t="n">
+      <c r="P64" t="n">
         <v>0.133063</v>
       </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
         <v>774.45</v>
       </c>
-      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4740,14 +4935,14 @@
         <v>0.13</v>
       </c>
       <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
         <v>86.98999999999999</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>54.35</v>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -4761,24 +4956,27 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
         <v>15.5</v>
       </c>
-      <c r="N65" t="n">
+      <c r="O65" t="n">
         <v>0.537471</v>
       </c>
-      <c r="O65" t="n">
+      <c r="P65" t="n">
         <v>-0.444875</v>
       </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
         <v>769.12</v>
       </c>
-      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4805,45 +5003,48 @@
         <v>-0</v>
       </c>
       <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
         <v>53.64</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>45.69</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>87.81</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>1395</v>
       </c>
-      <c r="J66" t="n">
-        <v>1</v>
-      </c>
       <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" t="n">
         <v>5</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>1613</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>12.5</v>
       </c>
-      <c r="N66" t="n">
+      <c r="O66" t="n">
         <v>0.107152</v>
       </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
         <v>-0.045869</v>
       </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
         <v>767.89</v>
       </c>
-      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4870,14 +5071,14 @@
         <v>-0.05</v>
       </c>
       <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
         <v>88.72</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>56.03</v>
       </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -4891,24 +5092,27 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
         <v>0.5</v>
       </c>
-      <c r="N67" t="n">
+      <c r="O67" t="n">
         <v>0.514423</v>
       </c>
-      <c r="O67" t="n">
+      <c r="P67" t="n">
         <v>-0.063779</v>
       </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
         <v>655.8200000000001</v>
       </c>
-      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4935,14 +5139,14 @@
         <v>-0.74</v>
       </c>
       <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
         <v>81.61</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>51.2</v>
       </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -4956,24 +5160,27 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
         <v>16.5</v>
       </c>
-      <c r="N68" t="n">
+      <c r="O68" t="n">
         <v>0.503655</v>
       </c>
-      <c r="O68" t="n">
+      <c r="P68" t="n">
         <v>-0.24306</v>
       </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
         <v>719.64</v>
       </c>
-      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5000,45 +5207,48 @@
         <v>-0.75</v>
       </c>
       <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
         <v>37.07</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>51.37</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>68.73</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>1346</v>
       </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
       <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
         <v>-21</v>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" t="n">
         <v>1381</v>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
         <v>-18.5</v>
       </c>
-      <c r="N69" t="n">
+      <c r="O69" t="n">
         <v>0.133063</v>
       </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
         <v>0.419785</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
         <v>751.92</v>
       </c>
-      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5065,14 +5275,14 @@
         <v>-0.84</v>
       </c>
       <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
         <v>74.78</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>49.77</v>
       </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -5086,24 +5296,27 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
         <v>23.5</v>
       </c>
-      <c r="N70" t="n">
+      <c r="O70" t="n">
         <v>0.549334</v>
       </c>
-      <c r="O70" t="n">
+      <c r="P70" t="n">
         <v>-0.162907</v>
       </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
         <v>672.14</v>
       </c>
-      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5130,14 +5343,14 @@
         <v>-0.84</v>
       </c>
       <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
         <v>74.94</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>49.05</v>
       </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -5151,24 +5364,27 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
         <v>28.167</v>
       </c>
-      <c r="N71" t="n">
+      <c r="O71" t="n">
         <v>0.573278</v>
       </c>
-      <c r="O71" t="n">
+      <c r="P71" t="n">
         <v>-0.158301</v>
       </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
         <v>652.5599999999999</v>
       </c>
-      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5195,45 +5411,48 @@
         <v>-0.88</v>
       </c>
       <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
         <v>44.05</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>45.71</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>84.89</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>1364</v>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
         <v>0.5</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>-14.5</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
         <v>1657</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>-4.583</v>
       </c>
-      <c r="N72" t="n">
+      <c r="O72" t="n">
         <v>0.180838</v>
       </c>
-      <c r="O72" t="n">
+      <c r="P72" t="n">
         <v>0.245148</v>
       </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
         <v>705.8099999999999</v>
       </c>
-      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5260,45 +5479,48 @@
         <v>-0.97</v>
       </c>
       <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
         <v>16.53</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>51.55</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>82.67</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>1471</v>
       </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
       <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
         <v>-38</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
         <v>1738</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>-10</v>
       </c>
-      <c r="N73" t="n">
+      <c r="O73" t="n">
         <v>-0.198543</v>
       </c>
-      <c r="O73" t="n">
+      <c r="P73" t="n">
         <v>0.292156</v>
       </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
         <v>623.79</v>
       </c>
-      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5325,45 +5547,48 @@
         <v>-0.98</v>
       </c>
       <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
         <v>23.27</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>45.88</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>88.64</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>1460</v>
       </c>
-      <c r="J74" t="n">
-        <v>1</v>
-      </c>
       <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="n">
         <v>10</v>
       </c>
-      <c r="L74" t="n">
+      <c r="M74" t="n">
         <v>1597</v>
       </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
       <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
         <v>0.022632</v>
       </c>
-      <c r="O74" t="n">
+      <c r="P74" t="n">
         <v>0.284185</v>
       </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
         <v>685.02</v>
       </c>
-      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5390,14 +5615,14 @@
         <v>-1</v>
       </c>
       <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
         <v>60.95</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>53.78</v>
       </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -5411,24 +5636,27 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
         <v>-6.167</v>
       </c>
-      <c r="N75" t="n">
+      <c r="O75" t="n">
         <v>0.227557</v>
       </c>
-      <c r="O75" t="n">
+      <c r="P75" t="n">
         <v>0.02711</v>
       </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
         <v>609.22</v>
       </c>
-      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5455,45 +5683,48 @@
         <v>-1.1</v>
       </c>
       <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
         <v>39.8</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>45.14</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>83.89</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>1404</v>
       </c>
-      <c r="J76" t="n">
-        <v>1</v>
-      </c>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
         <v>1563</v>
       </c>
-      <c r="M76" t="n">
+      <c r="N76" t="n">
         <v>7.5</v>
       </c>
-      <c r="N76" t="n">
+      <c r="O76" t="n">
         <v>0.052211</v>
       </c>
-      <c r="O76" t="n">
+      <c r="P76" t="n">
         <v>0.074022</v>
       </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
         <v>731.62</v>
       </c>
-      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5520,45 +5751,48 @@
         <v>-1.21</v>
       </c>
       <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
         <v>47.22</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>43.22</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>81.22</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>1516</v>
       </c>
-      <c r="J77" t="n">
-        <v>1</v>
-      </c>
       <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
         <v>19</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>1406</v>
       </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
         <v>12</v>
       </c>
-      <c r="N77" t="n">
+      <c r="O77" t="n">
         <v>0.241041</v>
       </c>
-      <c r="O77" t="n">
+      <c r="P77" t="n">
         <v>0.114871</v>
       </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
         <v>634.28</v>
       </c>
-      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5585,45 +5819,48 @@
         <v>-1.28</v>
       </c>
       <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
         <v>40.55</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>47.5</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>74.29000000000001</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>1576</v>
       </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
       <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
         <v>-10</v>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" t="n">
         <v>1439</v>
       </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
       <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
         <v>0.284185</v>
       </c>
-      <c r="O78" t="n">
+      <c r="P78" t="n">
         <v>0.022632</v>
       </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
         <v>556.26</v>
       </c>
-      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5650,45 +5887,48 @@
         <v>-1.75</v>
       </c>
       <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
         <v>11.31</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>49.9</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>83.56</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>1442</v>
       </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
       <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
         <v>-39</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
         <v>1763</v>
       </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
         <v>-17.167</v>
       </c>
-      <c r="N79" t="n">
+      <c r="O79" t="n">
         <v>-0.336134</v>
       </c>
-      <c r="O79" t="n">
+      <c r="P79" t="n">
         <v>0.332991</v>
       </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
         <v>609.75</v>
       </c>
-      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5715,45 +5955,48 @@
         <v>-1.89</v>
       </c>
       <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
         <v>44.22</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>44.69</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>70.95</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>1365</v>
       </c>
-      <c r="J80" t="n">
-        <v>1</v>
-      </c>
       <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="n">
         <v>7</v>
       </c>
-      <c r="L80" t="n">
+      <c r="M80" t="n">
         <v>1275</v>
       </c>
-      <c r="M80" t="n">
+      <c r="N80" t="n">
         <v>-14</v>
       </c>
-      <c r="N80" t="n">
+      <c r="O80" t="n">
         <v>0.125312</v>
       </c>
-      <c r="O80" t="n">
+      <c r="P80" t="n">
         <v>0.219087</v>
       </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
         <v>707.6</v>
       </c>
-      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5780,45 +6023,48 @@
         <v>-2.28</v>
       </c>
       <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
         <v>55.51</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>38.57</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>79.84999999999999</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>1564</v>
       </c>
-      <c r="J81" t="n">
-        <v>1</v>
-      </c>
       <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
         <v>31</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
         <v>1321</v>
       </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
         <v>20</v>
       </c>
-      <c r="N81" t="n">
+      <c r="O81" t="n">
         <v>0.218711</v>
       </c>
-      <c r="O81" t="n">
+      <c r="P81" t="n">
         <v>-0.052182</v>
       </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
         <v>568.1900000000001</v>
       </c>
-      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5845,45 +6091,48 @@
         <v>-2.8</v>
       </c>
       <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
         <v>37.79</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>44.33</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>73.66</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
         <v>1370</v>
       </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
       <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
         <v>-19</v>
       </c>
-      <c r="L82" t="n">
+      <c r="M82" t="n">
         <v>1480</v>
       </c>
-      <c r="M82" t="n">
+      <c r="N82" t="n">
         <v>-12</v>
       </c>
-      <c r="N82" t="n">
+      <c r="O82" t="n">
         <v>0.114871</v>
       </c>
-      <c r="O82" t="n">
+      <c r="P82" t="n">
         <v>0.241041</v>
       </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
         <v>660</v>
       </c>
-      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5910,14 +6159,14 @@
         <v>-2.85</v>
       </c>
       <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
         <v>72.75</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>42.13</v>
       </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -5931,24 +6180,27 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
         <v>27.833</v>
       </c>
-      <c r="N83" t="n">
+      <c r="O83" t="n">
         <v>0.351265</v>
       </c>
-      <c r="O83" t="n">
+      <c r="P83" t="n">
         <v>-0.256306</v>
       </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
         <v>745.61</v>
       </c>
-      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5975,45 +6227,48 @@
         <v>-2.86</v>
       </c>
       <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
         <v>29.49</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>40.21</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>1534</v>
       </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
       <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
         <v>-1</v>
       </c>
-      <c r="L84" t="n">
+      <c r="M84" t="n">
         <v>1690</v>
       </c>
-      <c r="M84" t="n">
+      <c r="N84" t="n">
         <v>26.5</v>
       </c>
-      <c r="N84" t="n">
+      <c r="O84" t="n">
         <v>-0.036869</v>
       </c>
-      <c r="O84" t="n">
+      <c r="P84" t="n">
         <v>0.235518</v>
       </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
         <v>572.2</v>
       </c>
-      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6040,45 +6295,48 @@
         <v>-2.87</v>
       </c>
       <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
         <v>18.43</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>46.35</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>83.92</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>1375</v>
       </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
       <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
         <v>-45</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
         <v>1802</v>
       </c>
-      <c r="M85" t="n">
+      <c r="N85" t="n">
         <v>-21.667</v>
       </c>
-      <c r="N85" t="n">
+      <c r="O85" t="n">
         <v>-0.167851</v>
       </c>
-      <c r="O85" t="n">
+      <c r="P85" t="n">
         <v>0.422096</v>
       </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
         <v>594.71</v>
       </c>
-      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6105,45 +6363,48 @@
         <v>-3.1</v>
       </c>
       <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
         <v>35.48</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>47.1</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>63.52</v>
       </c>
-      <c r="I86" t="n">
+      <c r="J86" t="n">
         <v>1338</v>
       </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
       <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
         <v>-35</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>1351</v>
       </c>
-      <c r="M86" t="n">
+      <c r="N86" t="n">
         <v>-35.667</v>
       </c>
-      <c r="N86" t="n">
+      <c r="O86" t="n">
         <v>0.065623</v>
       </c>
-      <c r="O86" t="n">
+      <c r="P86" t="n">
         <v>0.556279</v>
       </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
         <v>611.52</v>
       </c>
-      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6170,14 +6431,14 @@
         <v>-3.16</v>
       </c>
       <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
         <v>59.01</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>46.91</v>
       </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -6191,24 +6452,27 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
         <v>-10.167</v>
       </c>
-      <c r="N87" t="n">
+      <c r="O87" t="n">
         <v>0.372095</v>
       </c>
-      <c r="O87" t="n">
+      <c r="P87" t="n">
         <v>0.007618</v>
       </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
         <v>698.33</v>
       </c>
-      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6235,14 +6499,14 @@
         <v>-3.24</v>
       </c>
       <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
         <v>59.25</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>44.64</v>
       </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -6256,24 +6520,27 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
         <v>2.667</v>
       </c>
-      <c r="N88" t="n">
+      <c r="O88" t="n">
         <v>0.267286</v>
       </c>
-      <c r="O88" t="n">
+      <c r="P88" t="n">
         <v>-0.319818</v>
       </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
         <v>634.1900000000001</v>
       </c>
-      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6300,14 +6567,14 @@
         <v>-3.45</v>
       </c>
       <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="n">
         <v>66.91</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>39.8</v>
       </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -6321,24 +6588,27 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
         <v>29.5</v>
       </c>
-      <c r="N89" t="n">
+      <c r="O89" t="n">
         <v>0.59862</v>
       </c>
-      <c r="O89" t="n">
+      <c r="P89" t="n">
         <v>-0.238618</v>
       </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
         <v>543.02</v>
       </c>
-      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6365,45 +6635,48 @@
         <v>-3.53</v>
       </c>
       <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
         <v>66.86</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>39.36</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>52.56</v>
       </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
         <v>1562</v>
       </c>
-      <c r="J90" t="n">
-        <v>1</v>
-      </c>
       <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
         <v>26</v>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" t="n">
         <v>1494</v>
       </c>
-      <c r="M90" t="n">
+      <c r="N90" t="n">
         <v>7.917</v>
       </c>
-      <c r="N90" t="n">
+      <c r="O90" t="n">
         <v>0.238902</v>
       </c>
-      <c r="O90" t="n">
+      <c r="P90" t="n">
         <v>-0.313104</v>
       </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
         <v>515.59</v>
       </c>
-      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6430,45 +6703,48 @@
         <v>-3.69</v>
       </c>
       <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
         <v>42.37</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>40.24</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>78.02</v>
       </c>
-      <c r="I91" t="n">
+      <c r="J91" t="n">
         <v>1409</v>
       </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
       <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
         <v>-19</v>
       </c>
-      <c r="L91" t="n">
+      <c r="M91" t="n">
         <v>1563</v>
       </c>
-      <c r="M91" t="n">
+      <c r="N91" t="n">
         <v>6.833</v>
       </c>
-      <c r="N91" t="n">
+      <c r="O91" t="n">
         <v>0.139131</v>
       </c>
-      <c r="O91" t="n">
+      <c r="P91" t="n">
         <v>0.529351</v>
       </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
         <v>606.1799999999999</v>
       </c>
-      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6495,45 +6771,48 @@
         <v>-3.74</v>
       </c>
       <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
         <v>52.76</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>36.79</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>86.5</v>
       </c>
-      <c r="I92" t="n">
+      <c r="J92" t="n">
         <v>1378</v>
       </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
       <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
         <v>-10</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
         <v>1682</v>
       </c>
-      <c r="M92" t="n">
+      <c r="N92" t="n">
         <v>4.5</v>
       </c>
-      <c r="N92" t="n">
+      <c r="O92" t="n">
         <v>0.110655</v>
       </c>
-      <c r="O92" t="n">
+      <c r="P92" t="n">
         <v>-0.062746</v>
       </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
         <v>607.5599999999999</v>
       </c>
-      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6560,45 +6839,48 @@
         <v>-3.76</v>
       </c>
       <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
         <v>41.82</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>41.24</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>63.84</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
         <v>1416</v>
       </c>
-      <c r="J93" t="n">
-        <v>1</v>
-      </c>
       <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
         <v>3</v>
       </c>
-      <c r="L93" t="n">
+      <c r="M93" t="n">
         <v>1162</v>
       </c>
-      <c r="M93" t="n">
+      <c r="N93" t="n">
         <v>-13.167</v>
       </c>
-      <c r="N93" t="n">
+      <c r="O93" t="n">
         <v>0.156908</v>
       </c>
-      <c r="O93" t="n">
+      <c r="P93" t="n">
         <v>0.167962</v>
       </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
         <v>596.1900000000001</v>
       </c>
-      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6625,14 +6907,14 @@
         <v>-3.8</v>
       </c>
       <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
         <v>76.91</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>41.48</v>
       </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -6646,24 +6928,27 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
         <v>10.667</v>
       </c>
-      <c r="N94" t="n">
+      <c r="O94" t="n">
         <v>0.305366</v>
       </c>
-      <c r="O94" t="n">
+      <c r="P94" t="n">
         <v>-0.122199</v>
       </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
         <v>590.9400000000001</v>
       </c>
-      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6690,14 +6975,14 @@
         <v>-4.11</v>
       </c>
       <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
         <v>46.56</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>40.31</v>
       </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -6711,24 +6996,27 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
         <v>11.333</v>
       </c>
-      <c r="N95" t="n">
+      <c r="O95" t="n">
         <v>0.167908</v>
       </c>
-      <c r="O95" t="n">
+      <c r="P95" t="n">
         <v>0.168009</v>
       </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
         <v>573.38</v>
       </c>
-      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6755,45 +7043,48 @@
         <v>-4.32</v>
       </c>
       <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
         <v>45.46</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>38.41</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="I96" t="n">
+      <c r="J96" t="n">
         <v>1349</v>
       </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
       <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
         <v>-18</v>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" t="n">
         <v>1541</v>
       </c>
-      <c r="M96" t="n">
+      <c r="N96" t="n">
         <v>-7.5</v>
       </c>
-      <c r="N96" t="n">
+      <c r="O96" t="n">
         <v>0.125157</v>
       </c>
-      <c r="O96" t="n">
+      <c r="P96" t="n">
         <v>0.490713</v>
       </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
         <v>606.22</v>
       </c>
-      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6820,14 +7111,14 @@
         <v>-4.33</v>
       </c>
       <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
         <v>71.14</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>37.27</v>
       </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -6841,24 +7132,27 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
         <v>26.167</v>
       </c>
-      <c r="N97" t="n">
+      <c r="O97" t="n">
         <v>0.402182</v>
       </c>
-      <c r="O97" t="n">
+      <c r="P97" t="n">
         <v>-0.127677</v>
       </c>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
         <v>602.63</v>
       </c>
-      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6885,45 +7179,48 @@
         <v>-4.44</v>
       </c>
       <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
         <v>55.29</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>42.26</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>35.18</v>
       </c>
-      <c r="I98" t="n">
+      <c r="J98" t="n">
         <v>1432</v>
       </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
       <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
         <v>-26</v>
       </c>
-      <c r="L98" t="n">
+      <c r="M98" t="n">
         <v>1500</v>
       </c>
-      <c r="M98" t="n">
+      <c r="N98" t="n">
         <v>0.167</v>
       </c>
-      <c r="N98" t="n">
+      <c r="O98" t="n">
         <v>0.140922</v>
       </c>
-      <c r="O98" t="n">
+      <c r="P98" t="n">
         <v>0.054445</v>
       </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
         <v>602.83</v>
       </c>
-      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6950,14 +7247,14 @@
         <v>-4.53</v>
       </c>
       <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
         <v>58.03</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>39.15</v>
       </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -6971,24 +7268,27 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
         <v>9.5</v>
       </c>
-      <c r="N99" t="n">
+      <c r="O99" t="n">
         <v>0.170163</v>
       </c>
-      <c r="O99" t="n">
+      <c r="P99" t="n">
         <v>-0.022679</v>
       </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
         <v>631.0700000000001</v>
       </c>
-      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7015,45 +7315,48 @@
         <v>-4.57</v>
       </c>
       <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
         <v>33.05</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>42.16</v>
       </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>72.23</v>
       </c>
-      <c r="I100" t="n">
+      <c r="J100" t="n">
         <v>1252</v>
       </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
       <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
         <v>-45</v>
       </c>
-      <c r="L100" t="n">
+      <c r="M100" t="n">
         <v>1576</v>
       </c>
-      <c r="M100" t="n">
+      <c r="N100" t="n">
         <v>-28.667</v>
       </c>
-      <c r="N100" t="n">
+      <c r="O100" t="n">
         <v>0.114011</v>
       </c>
-      <c r="O100" t="n">
+      <c r="P100" t="n">
         <v>0.426656</v>
       </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
         <v>621.37</v>
       </c>
-      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7080,14 +7383,14 @@
         <v>-4.74</v>
       </c>
       <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="n">
         <v>88.86</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>35.08</v>
       </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
@@ -7101,24 +7404,27 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
         <v>31.167</v>
       </c>
-      <c r="N101" t="n">
+      <c r="O101" t="n">
         <v>0.607857</v>
       </c>
-      <c r="O101" t="n">
+      <c r="P101" t="n">
         <v>-0.070754</v>
       </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
         <v>621.61</v>
       </c>
-      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7145,45 +7451,48 @@
         <v>-4.77</v>
       </c>
       <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
         <v>30.05</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>40.64</v>
       </c>
-      <c r="H102" t="n">
+      <c r="I102" t="n">
         <v>75.61</v>
       </c>
-      <c r="I102" t="n">
+      <c r="J102" t="n">
         <v>1437.5</v>
       </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
       <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
         <v>-12.5</v>
       </c>
-      <c r="L102" t="n">
+      <c r="M102" t="n">
         <v>1478</v>
       </c>
-      <c r="M102" t="n">
+      <c r="N102" t="n">
         <v>-8.75</v>
       </c>
-      <c r="N102" t="n">
+      <c r="O102" t="n">
         <v>-0.00678</v>
       </c>
-      <c r="O102" t="n">
+      <c r="P102" t="n">
         <v>0.246843</v>
       </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
         <v>556.8200000000001</v>
       </c>
-      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7210,14 +7519,14 @@
         <v>-4.92</v>
       </c>
       <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
         <v>47.11</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>43.41</v>
       </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
@@ -7231,24 +7540,27 @@
         <v>0</v>
       </c>
       <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
         <v>-27.167</v>
       </c>
-      <c r="N103" t="n">
+      <c r="O103" t="n">
         <v>0.095341</v>
       </c>
-      <c r="O103" t="n">
+      <c r="P103" t="n">
         <v>0.033944</v>
       </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
         <v>543.98</v>
       </c>
-      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7275,14 +7587,14 @@
         <v>-5.03</v>
       </c>
       <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="n">
         <v>45.08</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>41.08</v>
       </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
@@ -7296,24 +7608,27 @@
         <v>0</v>
       </c>
       <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
         <v>-14.5</v>
       </c>
-      <c r="N104" t="n">
+      <c r="O104" t="n">
         <v>0.152314</v>
       </c>
-      <c r="O104" t="n">
+      <c r="P104" t="n">
         <v>-0.049521</v>
       </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
         <v>549.3099999999999</v>
       </c>
-      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7340,45 +7655,48 @@
         <v>-5.07</v>
       </c>
       <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="n">
         <v>47.61</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>40.15</v>
       </c>
-      <c r="H105" t="n">
+      <c r="I105" t="n">
         <v>35.09</v>
       </c>
-      <c r="I105" t="n">
+      <c r="J105" t="n">
         <v>1476</v>
       </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
       <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
         <v>-11</v>
       </c>
-      <c r="L105" t="n">
+      <c r="M105" t="n">
         <v>1326</v>
       </c>
-      <c r="M105" t="n">
+      <c r="N105" t="n">
         <v>6</v>
       </c>
-      <c r="N105" t="n">
+      <c r="O105" t="n">
         <v>0.143357</v>
       </c>
-      <c r="O105" t="n">
+      <c r="P105" t="n">
         <v>-0.037716</v>
       </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
         <v>561.42</v>
       </c>
-      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7405,14 +7723,14 @@
         <v>-5.16</v>
       </c>
       <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="n">
         <v>38.9</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>39.75</v>
       </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
@@ -7426,24 +7744,27 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
         <v>-8.667</v>
       </c>
-      <c r="N106" t="n">
+      <c r="O106" t="n">
         <v>0.025262</v>
       </c>
-      <c r="O106" t="n">
+      <c r="P106" t="n">
         <v>0.147051</v>
       </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
         <v>568.33</v>
       </c>
-      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7470,45 +7791,48 @@
         <v>-5.2</v>
       </c>
       <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>29.64</v>
       </c>
-      <c r="H107" t="n">
+      <c r="I107" t="n">
         <v>79.22</v>
       </c>
-      <c r="I107" t="n">
+      <c r="J107" t="n">
         <v>1327</v>
       </c>
-      <c r="J107" t="n">
-        <v>1</v>
-      </c>
       <c r="K107" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" t="n">
         <v>22</v>
       </c>
-      <c r="L107" t="n">
+      <c r="M107" t="n">
         <v>1363</v>
       </c>
-      <c r="M107" t="n">
+      <c r="N107" t="n">
         <v>19.333</v>
       </c>
-      <c r="N107" t="n">
+      <c r="O107" t="n">
         <v>0.301242</v>
       </c>
-      <c r="O107" t="n">
+      <c r="P107" t="n">
         <v>-0.025108</v>
       </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
         <v>640.3099999999999</v>
       </c>
-      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7535,45 +7859,48 @@
         <v>-5.36</v>
       </c>
       <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="n">
         <v>75.68000000000001</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>25.9</v>
       </c>
-      <c r="H108" t="n">
+      <c r="I108" t="n">
         <v>86.15000000000001</v>
       </c>
-      <c r="I108" t="n">
+      <c r="J108" t="n">
         <v>1451</v>
       </c>
-      <c r="J108" t="n">
-        <v>1</v>
-      </c>
       <c r="K108" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" t="n">
         <v>35</v>
       </c>
-      <c r="L108" t="n">
+      <c r="M108" t="n">
         <v>1438</v>
       </c>
-      <c r="M108" t="n">
+      <c r="N108" t="n">
         <v>35.667</v>
       </c>
-      <c r="N108" t="n">
+      <c r="O108" t="n">
         <v>0.556279</v>
       </c>
-      <c r="O108" t="n">
+      <c r="P108" t="n">
         <v>0.065623</v>
       </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
         <v>549.99</v>
       </c>
-      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7600,14 +7927,14 @@
         <v>-5.52</v>
       </c>
       <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="n">
         <v>61.17</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>36.64</v>
       </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
@@ -7621,24 +7948,27 @@
         <v>0</v>
       </c>
       <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
         <v>3.5</v>
       </c>
-      <c r="N109" t="n">
+      <c r="O109" t="n">
         <v>0.395767</v>
       </c>
-      <c r="O109" t="n">
+      <c r="P109" t="n">
         <v>-0.122854</v>
       </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
         <v>483.48</v>
       </c>
-      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7665,14 +7995,14 @@
         <v>-5.68</v>
       </c>
       <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="n">
         <v>54.74</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>39.73</v>
       </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
@@ -7686,24 +8016,27 @@
         <v>0</v>
       </c>
       <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
         <v>-20.333</v>
       </c>
-      <c r="N110" t="n">
+      <c r="O110" t="n">
         <v>0.218386</v>
       </c>
-      <c r="O110" t="n">
+      <c r="P110" t="n">
         <v>-0.209821</v>
       </c>
-      <c r="P110" t="n">
-        <v>0</v>
-      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
         <v>544.25</v>
       </c>
-      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7730,14 +8063,14 @@
         <v>-5.75</v>
       </c>
       <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="n">
         <v>66.7</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>32.61</v>
       </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
@@ -7751,24 +8084,27 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
         <v>24.5</v>
       </c>
-      <c r="N111" t="n">
+      <c r="O111" t="n">
         <v>0.288924</v>
       </c>
-      <c r="O111" t="n">
+      <c r="P111" t="n">
         <v>-0.248102</v>
       </c>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
         <v>502.86</v>
       </c>
-      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7795,45 +8131,48 @@
         <v>-5.81</v>
       </c>
       <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="n">
         <v>46.77</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>34.08</v>
       </c>
-      <c r="H112" t="n">
+      <c r="I112" t="n">
         <v>81.22</v>
       </c>
-      <c r="I112" t="n">
+      <c r="J112" t="n">
         <v>1401</v>
       </c>
-      <c r="J112" t="n">
+      <c r="K112" t="n">
         <v>0.5</v>
       </c>
-      <c r="K112" t="n">
+      <c r="L112" t="n">
         <v>-5</v>
       </c>
-      <c r="L112" t="n">
+      <c r="M112" t="n">
         <v>1548.5</v>
       </c>
-      <c r="M112" t="n">
+      <c r="N112" t="n">
         <v>14.417</v>
       </c>
-      <c r="N112" t="n">
+      <c r="O112" t="n">
         <v>0.165445</v>
       </c>
-      <c r="O112" t="n">
+      <c r="P112" t="n">
         <v>0.192613</v>
       </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
         <v>569.25</v>
       </c>
-      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7860,45 +8199,48 @@
         <v>-6.16</v>
       </c>
       <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="n">
         <v>32.55</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>37.22</v>
       </c>
-      <c r="H113" t="n">
+      <c r="I113" t="n">
         <v>62.22</v>
       </c>
-      <c r="I113" t="n">
+      <c r="J113" t="n">
         <v>1215</v>
       </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
       <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
         <v>-14</v>
       </c>
-      <c r="L113" t="n">
+      <c r="M113" t="n">
         <v>1240</v>
       </c>
-      <c r="M113" t="n">
+      <c r="N113" t="n">
         <v>-27.333</v>
       </c>
-      <c r="N113" t="n">
+      <c r="O113" t="n">
         <v>-0.070656</v>
       </c>
-      <c r="O113" t="n">
+      <c r="P113" t="n">
         <v>0.186432</v>
       </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
         <v>672.6900000000001</v>
       </c>
-      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7925,14 +8267,14 @@
         <v>-6.32</v>
       </c>
       <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="n">
         <v>66.56</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>34.16</v>
       </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
       <c r="I114" t="n">
         <v>0</v>
       </c>
@@ -7946,24 +8288,27 @@
         <v>0</v>
       </c>
       <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
         <v>1.5</v>
       </c>
-      <c r="N114" t="n">
+      <c r="O114" t="n">
         <v>0.401692</v>
       </c>
-      <c r="O114" t="n">
+      <c r="P114" t="n">
         <v>0.135652</v>
       </c>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
         <v>571.5</v>
       </c>
-      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7990,45 +8335,48 @@
         <v>-6.33</v>
       </c>
       <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="n">
         <v>35.36</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>33.41</v>
       </c>
-      <c r="H115" t="n">
+      <c r="I115" t="n">
         <v>78.38</v>
       </c>
-      <c r="I115" t="n">
+      <c r="J115" t="n">
         <v>1344</v>
       </c>
-      <c r="J115" t="n">
+      <c r="K115" t="n">
         <v>0.5</v>
       </c>
-      <c r="K115" t="n">
+      <c r="L115" t="n">
         <v>2.5</v>
       </c>
-      <c r="L115" t="n">
+      <c r="M115" t="n">
         <v>1447.5</v>
       </c>
-      <c r="M115" t="n">
+      <c r="N115" t="n">
         <v>-2.75</v>
       </c>
-      <c r="N115" t="n">
+      <c r="O115" t="n">
         <v>0.013787</v>
       </c>
-      <c r="O115" t="n">
+      <c r="P115" t="n">
         <v>0.035845</v>
       </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
         <v>580.64</v>
       </c>
-      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8055,14 +8403,14 @@
         <v>-6.51</v>
       </c>
       <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="n">
         <v>93.67</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>30.86</v>
       </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
@@ -8076,24 +8424,27 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
         <v>18.667</v>
       </c>
-      <c r="N116" t="n">
+      <c r="O116" t="n">
         <v>0.685814</v>
       </c>
-      <c r="O116" t="n">
+      <c r="P116" t="n">
         <v>-0.10615</v>
       </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
         <v>303.83</v>
       </c>
-      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8120,45 +8471,48 @@
         <v>-6.73</v>
       </c>
       <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="n">
         <v>45.9</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>30.99</v>
       </c>
-      <c r="H117" t="n">
+      <c r="I117" t="n">
         <v>76.42</v>
       </c>
-      <c r="I117" t="n">
+      <c r="J117" t="n">
         <v>1253</v>
       </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
       <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
         <v>-13</v>
       </c>
-      <c r="L117" t="n">
+      <c r="M117" t="n">
         <v>1508</v>
       </c>
-      <c r="M117" t="n">
+      <c r="N117" t="n">
         <v>7.833</v>
       </c>
-      <c r="N117" t="n">
+      <c r="O117" t="n">
         <v>0.182879</v>
       </c>
-      <c r="O117" t="n">
+      <c r="P117" t="n">
         <v>0.312247</v>
       </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
         <v>635.79</v>
       </c>
-      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8185,14 +8539,14 @@
         <v>-6.95</v>
       </c>
       <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>29.04</v>
       </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
@@ -8206,24 +8560,27 @@
         <v>0</v>
       </c>
       <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
         <v>20.667</v>
       </c>
-      <c r="N118" t="n">
+      <c r="O118" t="n">
         <v>0.506822</v>
       </c>
-      <c r="O118" t="n">
+      <c r="P118" t="n">
         <v>-0.06518599999999999</v>
       </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
         <v>573.83</v>
       </c>
-      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8250,45 +8607,48 @@
         <v>-7.05</v>
       </c>
       <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="n">
         <v>11.56</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>36.12</v>
       </c>
-      <c r="H119" t="n">
+      <c r="I119" t="n">
         <v>79.72</v>
       </c>
-      <c r="I119" t="n">
+      <c r="J119" t="n">
         <v>1268</v>
       </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
       <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
         <v>-50</v>
       </c>
-      <c r="L119" t="n">
+      <c r="M119" t="n">
         <v>1748</v>
       </c>
-      <c r="M119" t="n">
+      <c r="N119" t="n">
         <v>-10.833</v>
       </c>
-      <c r="N119" t="n">
+      <c r="O119" t="n">
         <v>-0.244122</v>
       </c>
-      <c r="O119" t="n">
+      <c r="P119" t="n">
         <v>0.351323</v>
       </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
         <v>549.92</v>
       </c>
-      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8315,45 +8675,48 @@
         <v>-7.06</v>
       </c>
       <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
         <v>39.86</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>34.39</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="n">
         <v>62.24</v>
       </c>
-      <c r="I120" t="n">
+      <c r="J120" t="n">
         <v>1309</v>
       </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
       <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
         <v>-22</v>
       </c>
-      <c r="L120" t="n">
+      <c r="M120" t="n">
         <v>1273</v>
       </c>
-      <c r="M120" t="n">
+      <c r="N120" t="n">
         <v>-19.333</v>
       </c>
-      <c r="N120" t="n">
+      <c r="O120" t="n">
         <v>-0.025108</v>
       </c>
-      <c r="O120" t="n">
+      <c r="P120" t="n">
         <v>0.301242</v>
       </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
         <v>528.29</v>
       </c>
-      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8380,45 +8743,48 @@
         <v>-7.4</v>
       </c>
       <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="n">
         <v>31.49</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>32.31</v>
       </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>74.33</v>
       </c>
-      <c r="I121" t="n">
+      <c r="J121" t="n">
         <v>1313</v>
       </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
       <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
         <v>-28</v>
       </c>
-      <c r="L121" t="n">
+      <c r="M121" t="n">
         <v>1538</v>
       </c>
-      <c r="M121" t="n">
+      <c r="N121" t="n">
         <v>-4.333</v>
       </c>
-      <c r="N121" t="n">
+      <c r="O121" t="n">
         <v>0.127526</v>
       </c>
-      <c r="O121" t="n">
+      <c r="P121" t="n">
         <v>0.492529</v>
       </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
         <v>522.84</v>
       </c>
-      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8445,45 +8811,48 @@
         <v>-7.47</v>
       </c>
       <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="n">
         <v>32.51</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>33.95</v>
       </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>71.23</v>
       </c>
-      <c r="I122" t="n">
+      <c r="J122" t="n">
         <v>1178</v>
       </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
       <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
         <v>-45</v>
       </c>
-      <c r="L122" t="n">
+      <c r="M122" t="n">
         <v>1562</v>
       </c>
-      <c r="M122" t="n">
+      <c r="N122" t="n">
         <v>-18.833</v>
       </c>
-      <c r="N122" t="n">
+      <c r="O122" t="n">
         <v>0.107901</v>
       </c>
-      <c r="O122" t="n">
+      <c r="P122" t="n">
         <v>0.621458</v>
       </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
         <v>593.36</v>
       </c>
-      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8510,14 +8879,14 @@
         <v>-7.51</v>
       </c>
       <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" t="n">
         <v>66.67</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>29.46</v>
       </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
@@ -8531,24 +8900,27 @@
         <v>0</v>
       </c>
       <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
         <v>5.333</v>
       </c>
-      <c r="N123" t="n">
+      <c r="O123" t="n">
         <v>0.233072</v>
       </c>
-      <c r="O123" t="n">
+      <c r="P123" t="n">
         <v>-0.123715</v>
       </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
         <v>589.89</v>
       </c>
-      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8575,45 +8947,48 @@
         <v>-7.76</v>
       </c>
       <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="n">
         <v>27.1</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>32.73</v>
       </c>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>71.33</v>
       </c>
-      <c r="I124" t="n">
+      <c r="J124" t="n">
         <v>1253</v>
       </c>
-      <c r="J124" t="n">
-        <v>0</v>
-      </c>
       <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
         <v>-31</v>
       </c>
-      <c r="L124" t="n">
+      <c r="M124" t="n">
         <v>1496</v>
       </c>
-      <c r="M124" t="n">
+      <c r="N124" t="n">
         <v>-20</v>
       </c>
-      <c r="N124" t="n">
+      <c r="O124" t="n">
         <v>-0.052182</v>
       </c>
-      <c r="O124" t="n">
+      <c r="P124" t="n">
         <v>0.218711</v>
       </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
         <v>540.01</v>
       </c>
-      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8640,45 +9015,48 @@
         <v>-7.89</v>
       </c>
       <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="n">
         <v>54.09</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>25.38</v>
       </c>
-      <c r="H125" t="n">
+      <c r="I125" t="n">
         <v>70.87</v>
       </c>
-      <c r="I125" t="n">
+      <c r="J125" t="n">
         <v>1265</v>
       </c>
-      <c r="J125" t="n">
-        <v>1</v>
-      </c>
       <c r="K125" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" t="n">
         <v>14</v>
       </c>
-      <c r="L125" t="n">
+      <c r="M125" t="n">
         <v>1240</v>
       </c>
-      <c r="M125" t="n">
+      <c r="N125" t="n">
         <v>27.333</v>
       </c>
-      <c r="N125" t="n">
+      <c r="O125" t="n">
         <v>0.186432</v>
       </c>
-      <c r="O125" t="n">
+      <c r="P125" t="n">
         <v>-0.070656</v>
       </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
         <v>622.84</v>
       </c>
-      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8705,14 +9083,14 @@
         <v>-8.02</v>
       </c>
       <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="n">
         <v>51.24</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>31.96</v>
       </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
@@ -8726,24 +9104,27 @@
         <v>0</v>
       </c>
       <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
         <v>-22.5</v>
       </c>
-      <c r="N126" t="n">
+      <c r="O126" t="n">
         <v>0.285997</v>
       </c>
-      <c r="O126" t="n">
+      <c r="P126" t="n">
         <v>0.375389</v>
       </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
         <v>576.77</v>
       </c>
-      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8770,14 +9151,14 @@
         <v>-8.08</v>
       </c>
       <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="n">
         <v>75.63</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>28.92</v>
       </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
@@ -8791,24 +9172,27 @@
         <v>0</v>
       </c>
       <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
         <v>-4.167</v>
       </c>
-      <c r="N127" t="n">
+      <c r="O127" t="n">
         <v>0.480273</v>
       </c>
-      <c r="O127" t="n">
+      <c r="P127" t="n">
         <v>0.052851</v>
       </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
         <v>195.68</v>
       </c>
-      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8835,45 +9219,48 @@
         <v>-8.25</v>
       </c>
       <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="n">
         <v>51.97</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>26.57</v>
       </c>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>70.45999999999999</v>
       </c>
-      <c r="I128" t="n">
+      <c r="J128" t="n">
         <v>1270</v>
       </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
       <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
         <v>-7</v>
       </c>
-      <c r="L128" t="n">
+      <c r="M128" t="n">
         <v>1360</v>
       </c>
-      <c r="M128" t="n">
+      <c r="N128" t="n">
         <v>14</v>
       </c>
-      <c r="N128" t="n">
+      <c r="O128" t="n">
         <v>0.219087</v>
       </c>
-      <c r="O128" t="n">
+      <c r="P128" t="n">
         <v>0.125312</v>
       </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
         <v>573.96</v>
       </c>
-      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8900,45 +9287,48 @@
         <v>-8.43</v>
       </c>
       <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>30.81</v>
       </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>84.04000000000001</v>
       </c>
-      <c r="I129" t="n">
+      <c r="J129" t="n">
         <v>1245</v>
       </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
       <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
         <v>-40</v>
       </c>
-      <c r="L129" t="n">
+      <c r="M129" t="n">
         <v>1791</v>
       </c>
-      <c r="M129" t="n">
+      <c r="N129" t="n">
         <v>-8.333</v>
       </c>
-      <c r="N129" t="n">
+      <c r="O129" t="n">
         <v>-0.331732</v>
       </c>
-      <c r="O129" t="n">
+      <c r="P129" t="n">
         <v>0.061317</v>
       </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
         <v>536.58</v>
       </c>
-      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8965,45 +9355,48 @@
         <v>-8.74</v>
       </c>
       <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="n">
         <v>24.98</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>30.39</v>
       </c>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>76.88</v>
       </c>
-      <c r="I130" t="n">
+      <c r="J130" t="n">
         <v>1143</v>
       </c>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
       <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
         <v>-51</v>
       </c>
-      <c r="L130" t="n">
+      <c r="M130" t="n">
         <v>1706</v>
       </c>
-      <c r="M130" t="n">
+      <c r="N130" t="n">
         <v>-10.333</v>
       </c>
-      <c r="N130" t="n">
+      <c r="O130" t="n">
         <v>-0.251351</v>
       </c>
-      <c r="O130" t="n">
+      <c r="P130" t="n">
         <v>0.387191</v>
       </c>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
         <v>585.76</v>
       </c>
-      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9030,14 +9423,14 @@
         <v>-9.06</v>
       </c>
       <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="n">
         <v>72.45</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>24.35</v>
       </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
@@ -9051,24 +9444,27 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
         <v>3.5</v>
       </c>
-      <c r="N131" t="n">
+      <c r="O131" t="n">
         <v>0.398895</v>
       </c>
-      <c r="O131" t="n">
+      <c r="P131" t="n">
         <v>-0.248119</v>
       </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
         <v>272.35</v>
       </c>
-      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9095,45 +9491,48 @@
         <v>-10.9</v>
       </c>
       <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="n">
         <v>47.19</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>18.42</v>
       </c>
-      <c r="H132" t="n">
+      <c r="I132" t="n">
         <v>74.83</v>
       </c>
-      <c r="I132" t="n">
+      <c r="J132" t="n">
         <v>1168</v>
       </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
       <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
         <v>-3</v>
       </c>
-      <c r="L132" t="n">
+      <c r="M132" t="n">
         <v>1422</v>
       </c>
-      <c r="M132" t="n">
+      <c r="N132" t="n">
         <v>13.167</v>
       </c>
-      <c r="N132" t="n">
+      <c r="O132" t="n">
         <v>0.167962</v>
       </c>
-      <c r="O132" t="n">
+      <c r="P132" t="n">
         <v>0.156908</v>
       </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
         <v>554.47</v>
       </c>
-      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9160,45 +9559,48 @@
         <v>-11.76</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
         <v>22.61</v>
       </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
         <v>87.06</v>
       </c>
-      <c r="I133" t="n">
+      <c r="J133" t="n">
         <v>1076</v>
       </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
       <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
         <v>-53</v>
       </c>
-      <c r="L133" t="n">
+      <c r="M133" t="n">
         <v>1925</v>
       </c>
-      <c r="M133" t="n">
+      <c r="N133" t="n">
         <v>-2.667</v>
       </c>
-      <c r="N133" t="n">
+      <c r="O133" t="n">
         <v>-0.242325</v>
       </c>
-      <c r="O133" t="n">
+      <c r="P133" t="n">
         <v>0.6666069999999999</v>
       </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
         <v>563.88</v>
       </c>
-      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9225,45 +9627,48 @@
         <v>-12.03</v>
       </c>
       <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="n">
         <v>52.12</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>19.43</v>
       </c>
-      <c r="H134" t="n">
+      <c r="I134" t="n">
         <v>38.85</v>
       </c>
-      <c r="I134" t="n">
+      <c r="J134" t="n">
         <v>1259</v>
       </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
       <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
         <v>-17</v>
       </c>
-      <c r="L134" t="n">
+      <c r="M134" t="n">
         <v>1537</v>
       </c>
-      <c r="M134" t="n">
+      <c r="N134" t="n">
         <v>10.917</v>
       </c>
-      <c r="N134" t="n">
+      <c r="O134" t="n">
         <v>0.288951</v>
       </c>
-      <c r="O134" t="n">
+      <c r="P134" t="n">
         <v>0.132627</v>
       </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
         <v>460.38</v>
       </c>
-      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9290,45 +9695,48 @@
         <v>-12.18</v>
       </c>
       <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="n">
         <v>21.09</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>22.59</v>
       </c>
-      <c r="H135" t="n">
+      <c r="I135" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="I135" t="n">
+      <c r="J135" t="n">
         <v>1035</v>
       </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
       <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
         <v>-57</v>
       </c>
-      <c r="L135" t="n">
+      <c r="M135" t="n">
         <v>1631</v>
       </c>
-      <c r="M135" t="n">
+      <c r="N135" t="n">
         <v>-21.167</v>
       </c>
-      <c r="N135" t="n">
+      <c r="O135" t="n">
         <v>-0.038077</v>
       </c>
-      <c r="O135" t="n">
+      <c r="P135" t="n">
         <v>0.683177</v>
       </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
         <v>522.83</v>
       </c>
-      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9355,45 +9763,48 @@
         <v>-12.65</v>
       </c>
       <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="n">
         <v>18.96</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>21.93</v>
       </c>
-      <c r="H136" t="n">
+      <c r="I136" t="n">
         <v>65.73</v>
       </c>
-      <c r="I136" t="n">
+      <c r="J136" t="n">
         <v>1058</v>
       </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
       <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
         <v>-49</v>
       </c>
-      <c r="L136" t="n">
+      <c r="M136" t="n">
         <v>1478</v>
       </c>
-      <c r="M136" t="n">
+      <c r="N136" t="n">
         <v>-20.5</v>
       </c>
-      <c r="N136" t="n">
+      <c r="O136" t="n">
         <v>-0.025209</v>
       </c>
-      <c r="O136" t="n">
+      <c r="P136" t="n">
         <v>0.638028</v>
       </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
         <v>505.49</v>
       </c>
-      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9420,45 +9831,48 @@
         <v>-15.65</v>
       </c>
       <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="n">
         <v>60.5</v>
       </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
       <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
         <v>82.23999999999999</v>
       </c>
-      <c r="I137" t="n">
+      <c r="J137" t="n">
         <v>1049</v>
       </c>
-      <c r="J137" t="n">
-        <v>1</v>
-      </c>
       <c r="K137" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" t="n">
         <v>16</v>
       </c>
-      <c r="L137" t="n">
+      <c r="M137" t="n">
         <v>1479</v>
       </c>
-      <c r="M137" t="n">
+      <c r="N137" t="n">
         <v>45.333</v>
       </c>
-      <c r="N137" t="n">
+      <c r="O137" t="n">
         <v>0.329973</v>
       </c>
-      <c r="O137" t="n">
+      <c r="P137" t="n">
         <v>0.203096</v>
       </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
         <v>525.9400000000001</v>
       </c>
-      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9485,45 +9899,48 @@
         <v>-16.64</v>
       </c>
       <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="n">
         <v>37.88</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>4.62</v>
       </c>
-      <c r="H138" t="n">
+      <c r="I138" t="n">
         <v>73.84</v>
       </c>
-      <c r="I138" t="n">
+      <c r="J138" t="n">
         <v>905</v>
       </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
       <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
         <v>-22</v>
       </c>
-      <c r="L138" t="n">
+      <c r="M138" t="n">
         <v>1520</v>
       </c>
-      <c r="M138" t="n">
+      <c r="N138" t="n">
         <v>5.5</v>
       </c>
-      <c r="N138" t="n">
+      <c r="O138" t="n">
         <v>0.021979</v>
       </c>
-      <c r="O138" t="n">
+      <c r="P138" t="n">
         <v>0.477589</v>
       </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
         <v>546.84</v>
       </c>
-      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10936,7 +11353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11005,196 +11422,216 @@
         <v>0.949</v>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>early_season_shrink_games</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>min_rating_scale</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>coefficient_points</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>avg_opponent_postgame_elo</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6.9522</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>avg_team_pregame_elo</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>6.1382</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>talent</t>
+          <t>avg_opponent_postgame_elo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.198</v>
+        <v>6.9522</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>recent_win_pct</t>
+          <t>avg_team_pregame_elo</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.937</v>
+        <v>6.1382</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>recent_fbs_win_pct</t>
+          <t>talent</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-2.8463</v>
+        <v>4.198</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>latest_team_postgame_elo</t>
+          <t>recent_win_pct</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-2.3627</v>
+        <v>2.937</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fbs_avg_margin</t>
+          <t>recent_fbs_win_pct</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8701</v>
+        <v>-2.8463</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>recent_fbs_avg_margin</t>
+          <t>latest_team_postgame_elo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8701</v>
+        <v>-2.3627</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>avg_team_postgame_elo</t>
+          <t>fbs_avg_margin</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.5903</v>
+        <v>1.8701</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>offense_success_rate</t>
+          <t>recent_fbs_avg_margin</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3442</v>
+        <v>1.8701</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>recent_avg_cover_margin</t>
+          <t>avg_team_postgame_elo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.2197</v>
+        <v>-1.5903</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>avg_cover_margin</t>
+          <t>offense_success_rate</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.2197</v>
+        <v>1.3442</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>defense_ppa_allowed</t>
+          <t>recent_avg_cover_margin</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2089</v>
+        <v>-1.2197</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>defense_success_rate_allowed</t>
+          <t>avg_cover_margin</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.9149</v>
+        <v>-1.2197</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>offense_ppa</t>
+          <t>defense_ppa_allowed</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8848</v>
+        <v>1.2089</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fbs_avg_opponent_pregame_elo</t>
+          <t>defense_success_rate_allowed</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7018</v>
+        <v>-0.9149</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>wepa_total</t>
+          <t>offense_ppa</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.8848</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>fbs_avg_opponent_pregame_elo</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.7018</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>wepa_total</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>wepa_allowed_total</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B28" t="n">
         <v>0</v>
       </c>
     </row>
